--- a/Data/collapsed database manual cases/bajasur_collapsed_edited.xlsx
+++ b/Data/collapsed database manual cases/bajasur_collapsed_edited.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpzorrilla/Documents/GitHub/The-Mexican-municipal-elections-electoral-precinct-level-database/Data/collapsed database manual cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605EEB5F-65A5-0E47-B50D-A7637B9ED0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D81B57-489A-4342-B72D-AF8F071516B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4480" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="134">
   <si>
     <t>uniqueid</t>
   </si>
@@ -397,6 +397,36 @@
   </si>
   <si>
     <t>Carlos Mendoza Davis</t>
+  </si>
+  <si>
+    <t>UC</t>
+  </si>
+  <si>
+    <t>EDITH AGUILAR VILLAVICENCIO</t>
+  </si>
+  <si>
+    <t>PAOLA MARGARITA COTA DAVIS</t>
+  </si>
+  <si>
+    <t>JHHEBCS</t>
+  </si>
+  <si>
+    <t>ILIANA GUADALUPE TALAMANTES HIGUERA</t>
+  </si>
+  <si>
+    <t>MILENA PAOLA QUIROGA ROMERO</t>
+  </si>
+  <si>
+    <t>OSCAR LEGGS CASTRO</t>
+  </si>
+  <si>
+    <t>https://www.google.com/url?sa=t&amp;source=web&amp;rct=j&amp;opi=89978449&amp;url=https://zetatijuana.com/2021/06/iliana-talamantes-sera-la-primera-la-alcaldesa-en-la-historia-de-comondu/&amp;ved=2ahUKEwjSueigsreTAxUeIUQIHTk_KekQFnoECCEQAQ&amp;usg=AOvVaw0dKqGt5Kxf0sIay22qmf2j</t>
+  </si>
+  <si>
+    <t>https://www.cbcs.gob.mx/index.php/diputados-morena/xv-legislatura/dip-milena-paola-quiroga-romero</t>
+  </si>
+  <si>
+    <t>https://www.eluniversal.com.mx/estados/exalcalde-de-los-cabos-oscar-leggs-se-destapa-para-la-gubernatura-de-bcs-en-2027-es-investigado-por-desfalco-de-14-mdp/</t>
   </si>
 </sst>
 </file>
@@ -768,7 +798,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
@@ -2319,6 +2349,100 @@
         <v>123</v>
       </c>
     </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>3002</v>
+      </c>
+      <c r="B34">
+        <v>2024</v>
+      </c>
+      <c r="E34" t="s">
+        <v>124</v>
+      </c>
+      <c r="H34" t="s">
+        <v>124</v>
+      </c>
+      <c r="K34" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>3009</v>
+      </c>
+      <c r="B35">
+        <v>2024</v>
+      </c>
+      <c r="E35" t="s">
+        <v>124</v>
+      </c>
+      <c r="H35" t="s">
+        <v>124</v>
+      </c>
+      <c r="K35" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>3001</v>
+      </c>
+      <c r="B36">
+        <v>2024</v>
+      </c>
+      <c r="E36" t="s">
+        <v>127</v>
+      </c>
+      <c r="F36" t="s">
+        <v>128</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I36" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>3003</v>
+      </c>
+      <c r="B37">
+        <v>2024</v>
+      </c>
+      <c r="E37" t="s">
+        <v>127</v>
+      </c>
+      <c r="F37" t="s">
+        <v>129</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I37" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>3008</v>
+      </c>
+      <c r="B38">
+        <v>2024</v>
+      </c>
+      <c r="E38" t="s">
+        <v>127</v>
+      </c>
+      <c r="F38" t="s">
+        <v>130</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I38" t="s">
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S31" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="6">
